--- a/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
+++ b/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
@@ -186,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -321,11 +321,118 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="000284C7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -458,6 +565,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -786,15 +903,6 @@
           <t>THORNFIELD LIFE SCIENCES MARKETING</t>
         </is>
       </c>
-      <c r="B1" s="14" t="n"/>
-      <c r="C1" s="14" t="n"/>
-      <c r="D1" s="14" t="n"/>
-      <c r="E1" s="14" t="n"/>
-      <c r="F1" s="14" t="n"/>
-      <c r="G1" s="14" t="n"/>
-      <c r="H1" s="14" t="n"/>
-      <c r="I1" s="14" t="n"/>
-      <c r="J1" s="14" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="15" t="inlineStr">
@@ -802,15 +910,6 @@
           <t>Q1 2026 Campaign Budget Worksheet</t>
         </is>
       </c>
-      <c r="B2" s="15" t="n"/>
-      <c r="C2" s="15" t="n"/>
-      <c r="D2" s="15" t="n"/>
-      <c r="E2" s="15" t="n"/>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="15" t="n"/>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="15" t="n"/>
-      <c r="J2" s="15" t="n"/>
     </row>
     <row r="3" ht="10" customHeight="1"/>
     <row r="4" ht="20" customHeight="1">
@@ -819,19 +918,19 @@
           <t>Document owner:</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>Ted Kowalczyk, VP, Paid Media</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
-      <c r="E4" s="17" t="n"/>
-      <c r="F4" s="17" t="n"/>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="17" t="n"/>
-      <c r="I4" s="17" t="n"/>
-      <c r="J4" s="18" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="47" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
@@ -839,19 +938,12 @@
           <t>File:</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Q1_2026_campaign_budget_worksheet.xlsx</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="21" t="n"/>
+      <c r="J5" s="48" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -859,19 +951,12 @@
           <t>Version:</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="21" t="n"/>
+      <c r="J6" s="48" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
@@ -879,19 +964,12 @@
           <t>Issued:</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>12/22/2025</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="21" t="n"/>
+      <c r="J7" s="48" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="19" t="inlineStr">
@@ -899,19 +977,12 @@
           <t>Status:</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Open — Q1 2026 in progress</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="21" t="n"/>
+      <c r="J8" s="48" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
@@ -919,19 +990,12 @@
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Paid Media (Ted Kowalczyk) with input from Client Strategy (Sofia Bergen) and Analytics &amp; Reporting (Grace Feldman)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="21" t="n"/>
+      <c r="J9" s="48" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
@@ -939,36 +1003,36 @@
           <t>Anchor period:</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>January 1, 2026 – March 31, 2026</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="23" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="23" t="n"/>
-      <c r="H10" s="23" t="n"/>
-      <c r="I10" s="23" t="n"/>
-      <c r="J10" s="24" t="n"/>
+      <c r="C10" s="49" t="n"/>
+      <c r="D10" s="49" t="n"/>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="50" t="n"/>
     </row>
     <row r="11" ht="12" customHeight="1"/>
     <row r="12" ht="56" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>Planning worksheet for all Q1 2026 paid-media line items across the combined Thornfield / inherited-Bramwell book of business. Line items are booked at the placement level (client × channel × vendor) and expressed as planned monthly gross media spend. All figures in USD. Campaign IDs follow the CMP-YYYY-#### convention introduced with the January 1, 2026 unified taxonomy cutover; the legacy BW- prefix strings are retired for Q1 2026 continuations and are not shown here.</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="27" t="n"/>
+      <c r="A12" s="51" t="inlineStr">
+        <is>
+          <t>Planning worksheet for the priority Q1 2026 paid-media placements actively managed and budgeted at the individual-campaign level for named strategic accounts (Ashford, Caldwell, Northlake, Fenwick, Marlstone, Wrenfield), the MedTech AdNetwork programmatic placement, and several multi-client vertical/roll-up lines. This worksheet does not itemize every client account in the combined Thornfield / inherited-Bramwell book of business; the remaining accounts' platform spend is tracked and totaled by client in the managed-spend exports rather than line-itemized here. Line items are booked at the placement level (client x channel x vendor) and expressed as planned monthly gross media spend. All figures in USD. Campaign IDs follow the CMP-YYYY-#### convention introduced with the January 1, 2026 unified taxonomy cutover; the legacy BW- prefix strings are retired for Q1 2026 continuations and are not shown here.</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="52" t="n"/>
+      <c r="I12" s="52" t="n"/>
+      <c r="J12" s="53" t="n"/>
     </row>
     <row r="13" ht="14" customHeight="1"/>
     <row r="14" ht="26" customHeight="1">
@@ -977,15 +1041,6 @@
           <t>Line items</t>
         </is>
       </c>
-      <c r="B14" s="28" t="n"/>
-      <c r="C14" s="28" t="n"/>
-      <c r="D14" s="28" t="n"/>
-      <c r="E14" s="28" t="n"/>
-      <c r="F14" s="28" t="n"/>
-      <c r="G14" s="28" t="n"/>
-      <c r="H14" s="28" t="n"/>
-      <c r="I14" s="28" t="n"/>
-      <c r="J14" s="28" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="29" t="inlineStr">
@@ -2231,7 +2286,7 @@
       </c>
       <c r="J41" s="41" t="inlineStr">
         <is>
-          <t>Planned gross media spend, all lines</t>
+          <t>Planned gross media spend, named lines above only — not the full managed-spend book; see the Q1 2026 managed-spend export for platform-level totals by client.</t>
         </is>
       </c>
     </row>
@@ -2242,15 +2297,6 @@
           <t>Footnotes</t>
         </is>
       </c>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="43" t="n"/>
-      <c r="E43" s="43" t="n"/>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="43" t="n"/>
-      <c r="H43" s="43" t="n"/>
-      <c r="I43" s="43" t="n"/>
-      <c r="J43" s="43" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="44" t="inlineStr">
@@ -2258,15 +2304,6 @@
           <t>1. All amounts are planned gross media spend at the placement level and exclude Thornfield's management fee, agency creative production, and applicable platform fees invoiced separately.</t>
         </is>
       </c>
-      <c r="B44" s="44" t="n"/>
-      <c r="C44" s="44" t="n"/>
-      <c r="D44" s="44" t="n"/>
-      <c r="E44" s="44" t="n"/>
-      <c r="F44" s="44" t="n"/>
-      <c r="G44" s="44" t="n"/>
-      <c r="H44" s="44" t="n"/>
-      <c r="I44" s="44" t="n"/>
-      <c r="J44" s="44" t="n"/>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="44" t="inlineStr">
@@ -2274,15 +2311,6 @@
           <t>2. Line items reflect the Thornfield unified taxonomy effective January 1, 2026. Legacy BW- prefixed strings still visible in prior-quarter attribution history have been remapped to their Q1 2026 successor Campaign IDs above by the Analytics &amp; Reporting mapping table.</t>
         </is>
       </c>
-      <c r="B45" s="44" t="n"/>
-      <c r="C45" s="44" t="n"/>
-      <c r="D45" s="44" t="n"/>
-      <c r="E45" s="44" t="n"/>
-      <c r="F45" s="44" t="n"/>
-      <c r="G45" s="44" t="n"/>
-      <c r="H45" s="44" t="n"/>
-      <c r="I45" s="44" t="n"/>
-      <c r="J45" s="44" t="n"/>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="44" t="inlineStr">
@@ -2290,15 +2318,6 @@
           <t>3. Owner column defaults to Ted Kowalczyk, VP Paid Media, in his capacity as document owner for Q1 2026 planning; day-to-day execution is delegated within the Paid Media team by channel pod.</t>
         </is>
       </c>
-      <c r="B46" s="44" t="n"/>
-      <c r="C46" s="44" t="n"/>
-      <c r="D46" s="44" t="n"/>
-      <c r="E46" s="44" t="n"/>
-      <c r="F46" s="44" t="n"/>
-      <c r="G46" s="44" t="n"/>
-      <c r="H46" s="44" t="n"/>
-      <c r="I46" s="44" t="n"/>
-      <c r="J46" s="44" t="n"/>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="44" t="inlineStr">
@@ -2306,15 +2325,6 @@
           <t>4. The Q1 2026 Monthly column reflects the flat monthly plan where applicable; lines with a per-month schedule that varies across the quarter (e.g., trade-show support with a Feb flight) show "(varies)" and should be read from the Jan / Feb / Mar columns directly.</t>
         </is>
       </c>
-      <c r="B47" s="44" t="n"/>
-      <c r="C47" s="44" t="n"/>
-      <c r="D47" s="44" t="n"/>
-      <c r="E47" s="44" t="n"/>
-      <c r="F47" s="44" t="n"/>
-      <c r="G47" s="44" t="n"/>
-      <c r="H47" s="44" t="n"/>
-      <c r="I47" s="44" t="n"/>
-      <c r="J47" s="44" t="n"/>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="44" t="inlineStr">
@@ -2322,15 +2332,6 @@
           <t>5. This worksheet does not restate contractual terms carried on individual vendor insertion orders or client MSAs; refer to the applicable IO or MSA on file for those terms.</t>
         </is>
       </c>
-      <c r="B48" s="44" t="n"/>
-      <c r="C48" s="44" t="n"/>
-      <c r="D48" s="44" t="n"/>
-      <c r="E48" s="44" t="n"/>
-      <c r="F48" s="44" t="n"/>
-      <c r="G48" s="44" t="n"/>
-      <c r="H48" s="44" t="n"/>
-      <c r="I48" s="44" t="n"/>
-      <c r="J48" s="44" t="n"/>
     </row>
     <row r="49" ht="12" customHeight="1"/>
     <row r="50" ht="22" customHeight="1">
@@ -2339,15 +2340,6 @@
           <t>End of worksheet.</t>
         </is>
       </c>
-      <c r="B50" s="45" t="n"/>
-      <c r="C50" s="45" t="n"/>
-      <c r="D50" s="45" t="n"/>
-      <c r="E50" s="45" t="n"/>
-      <c r="F50" s="45" t="n"/>
-      <c r="G50" s="45" t="n"/>
-      <c r="H50" s="45" t="n"/>
-      <c r="I50" s="45" t="n"/>
-      <c r="J50" s="45" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
+++ b/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
@@ -186,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -428,11 +428,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -575,6 +590,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -918,7 +939,7 @@
           <t>Document owner:</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
         <is>
           <t>Ted Kowalczyk, VP, Paid Media</t>
         </is>
@@ -938,7 +959,7 @@
           <t>File:</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>Q1_2026_campaign_budget_worksheet.xlsx</t>
         </is>
@@ -951,7 +972,7 @@
           <t>Version:</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B6" s="55" t="inlineStr">
         <is>
           <t>v1.0</t>
         </is>
@@ -964,7 +985,7 @@
           <t>Issued:</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="55" t="inlineStr">
         <is>
           <t>12/22/2025</t>
         </is>
@@ -977,7 +998,7 @@
           <t>Status:</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="55" t="inlineStr">
         <is>
           <t>Open — Q1 2026 in progress</t>
         </is>
@@ -990,7 +1011,7 @@
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="55" t="inlineStr">
         <is>
           <t>Paid Media (Ted Kowalczyk) with input from Client Strategy (Sofia Bergen) and Analytics &amp; Reporting (Grace Feldman)</t>
         </is>
@@ -1000,7 +1021,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Anchor period:</t>
+          <t>Reporting period:</t>
         </is>
       </c>
       <c r="B10" s="24" t="inlineStr">

--- a/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
+++ b/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -137,6 +137,12 @@
       <color rgb="0094A3B8"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF334155"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -447,7 +453,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -594,6 +600,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2356,7 +2365,7 @@
     </row>
     <row r="49" ht="12" customHeight="1"/>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="A50" s="56" t="inlineStr">
         <is>
           <t>End of worksheet.</t>
         </is>

--- a/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
+++ b/filesystem/MarketingOps/Budgets/Q1_2026_campaign_budget_worksheet.xlsx
@@ -1051,7 +1051,7 @@
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="51" t="inlineStr">
         <is>
-          <t>Planning worksheet for the priority Q1 2026 paid-media placements actively managed and budgeted at the individual-campaign level for named strategic accounts (Ashford, Caldwell, Northlake, Fenwick, Marlstone, Wrenfield), the MedTech AdNetwork programmatic placement, and several multi-client vertical/roll-up lines. This worksheet does not itemize every client account in the combined Thornfield / inherited-Bramwell book of business; the remaining accounts' platform spend is tracked and totaled by client in the managed-spend exports rather than line-itemized here. Line items are booked at the placement level (client x channel x vendor) and expressed as planned monthly gross media spend. All figures in USD. Campaign IDs follow the CMP-YYYY-#### convention introduced with the January 1, 2026 unified taxonomy cutover; the legacy BW- prefix strings are retired for Q1 2026 continuations and are not shown here.</t>
+          <t>Planning worksheet for the priority Q1 2026 paid-media placements actively managed and budgeted at the individual-campaign level for named strategic accounts (Ashford, Caldwell, Northlake, Fenwick, Marlstone, Wrenfield, Larchfield), and several multi-client vertical/roll-up lines. Larchfield Bioanalytics' MedTech AdNetwork programmatic placement (CMP-2026-0012) was migrated off its legacy multi-account roll-up naming to a named-account line per the Campaign Taxonomy &amp; Migration Guide (Section 3). This worksheet does not itemize every client account in the combined Thornfield / inherited-Bramwell book of business; the remaining accounts' platform spend is tracked and totaled by client in the managed-spend exports rather than line-itemized here. Line items are booked at the placement level (client x channel x vendor) and expressed as planned monthly gross media spend. All figures in USD. Campaign IDs follow the CMP-YYYY-#### convention introduced with the January 1, 2026 unified taxonomy cutover; the legacy BW- prefix strings are retired for Q1 2026 continuations and are not shown here.</t>
         </is>
       </c>
       <c r="B12" s="52" t="n"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B27" s="37" t="inlineStr">
         <is>
-          <t>Life Sciences OEM — Programmatic Display</t>
+          <t>Larchfield Bioanalytics — Programmatic Display</t>
         </is>
       </c>
       <c r="C27" s="37" t="inlineStr">
